--- a/zy70922/output/report.xlsx
+++ b/zy70922/output/report.xlsx
@@ -410,7 +410,7 @@
         <v>对账ID</v>
       </c>
       <c r="B2" t="str">
-        <v>38cf6839-4d99-4421-882b-a2761e01b114</v>
+        <v>2d93a8a8-03f7-45d9-9558-de94c47b3444</v>
       </c>
     </row>
     <row r="3">
@@ -418,7 +418,7 @@
         <v>生成时间</v>
       </c>
       <c r="B3" t="str">
-        <v>2026/5/26 23:31:00</v>
+        <v>2026/5/27 00:39:13</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>合格率</v>
       </c>
       <c r="B7" t="str">
-        <v>75%</v>
+        <v>63%</v>
       </c>
     </row>
     <row r="8">
@@ -450,7 +450,7 @@
         <v>差异总数</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -458,7 +458,7 @@
         <v>已解决差异</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -466,7 +466,7 @@
         <v>待复核</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -523,7 +523,7 @@
         <v>S202405001</v>
       </c>
       <c r="B2" t="str">
-        <v>已放行</v>
+        <v>比对通过</v>
       </c>
       <c r="C2" t="str">
         <v>重金属-铅</v>
@@ -553,7 +553,7 @@
         <v>所有检测项目合格，无差异，予以放行</v>
       </c>
       <c r="L2" t="str">
-        <v>2026/5/26 23:31:00</v>
+        <v>2026/5/27 00:39:13</v>
       </c>
     </row>
     <row r="3">
@@ -637,7 +637,7 @@
         <v>S202405002</v>
       </c>
       <c r="B5" t="str">
-        <v>需补材料</v>
+        <v>比对不通过</v>
       </c>
       <c r="C5" t="str">
         <v>农药残留-有机磷</v>
@@ -667,7 +667,7 @@
         <v>有机磷农药残留超标（0.08mg/kg &gt; 标准0.05mg/kg），需合作社提供农药使用记录并安排复检</v>
       </c>
       <c r="L5" t="str">
-        <v>2026/5/26 23:31:00</v>
+        <v>2026/5/27 00:39:13</v>
       </c>
     </row>
     <row r="6">
@@ -713,7 +713,7 @@
         <v>S202405003</v>
       </c>
       <c r="B7" t="str">
-        <v>已放行</v>
+        <v>比对不通过</v>
       </c>
       <c r="C7" t="str">
         <v>重金属-铅</v>
@@ -722,13 +722,13 @@
         <v>不合格</v>
       </c>
       <c r="E7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="F7" t="str">
-        <v>检测值超标</v>
+        <v>复检窗口超时</v>
       </c>
       <c r="G7" t="str">
-        <v>样品 S202405003 的 重金属-铅 检测值超出标准范围</v>
+        <v>样品 S202405003 的 重金属-铅 复检超出规定时间窗口</v>
       </c>
       <c r="H7" t="str">
         <v>是</v>
@@ -740,10 +740,10 @@
         <v>接样员张三</v>
       </c>
       <c r="K7" t="str">
-        <v>复检超窗口原因为仪器故障维修，经质量负责人批准后予以放行，复检结果合格（0.15mg/kg为初检结果，复检0.08mg/kg合格）</v>
+        <v>复检超窗口原因为仪器故障维修，经质量负责人批准后予以放行。初检0.15mg/kg不合格，复检0.08mg/kg合格</v>
       </c>
       <c r="L7" t="str">
-        <v>2026/5/26 23:31:00</v>
+        <v>2026/5/27 00:39:13</v>
       </c>
     </row>
     <row r="8">
@@ -754,22 +754,22 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>农药残留-有机磷</v>
+        <v>重金属-铅</v>
       </c>
       <c r="D8" t="str">
         <v>合格</v>
       </c>
       <c r="E8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>复检窗口超时</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>样品 S202405003 的 重金属-铅 复检超出规定时间窗口</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -786,13 +786,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>S202405004</v>
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>比对通过</v>
+        <v/>
       </c>
       <c r="C9" t="str">
-        <v>重金属-镉</v>
+        <v>农药残留-有机磷</v>
       </c>
       <c r="D9" t="str">
         <v>合格</v>
@@ -801,13 +801,13 @@
         <v>否</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>检测值超标</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>样品 S202405003 的 重金属-铅 检测值超出标准范围</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -830,22 +830,22 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>农药残留-有机磷</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>合格</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>否</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>检测项目不匹配</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>样品 S202405003 的 重金属-铅 触发复检规则但未进行复检</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -862,28 +862,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>S202405005</v>
+        <v/>
       </c>
       <c r="B11" t="str">
-        <v>比对通过</v>
+        <v/>
       </c>
       <c r="C11" t="str">
-        <v>重金属-铅</v>
+        <v/>
       </c>
       <c r="D11" t="str">
-        <v>合格</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>否</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>样品混批</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>样品 S202405003 存在混批情况，涉及批次: BATCH20240501, BATCH20240502</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -900,13 +900,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>S202405004</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>比对通过</v>
       </c>
       <c r="C12" t="str">
-        <v>农药残留-拟除虫菊酯</v>
+        <v>重金属-镉</v>
       </c>
       <c r="D12" t="str">
         <v>合格</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>S202405006</v>
+        <v/>
       </c>
       <c r="B13" t="str">
-        <v>比对不通过</v>
+        <v/>
       </c>
       <c r="C13" t="str">
         <v>农药残留-有机磷</v>
       </c>
       <c r="D13" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
       <c r="E13" t="str">
         <v>否</v>
       </c>
       <c r="F13" t="str">
-        <v>检测值超标</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>样品 S202405006 的 农药残留-有机磷 检测值超出标准范围</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>否</v>
+        <v/>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -976,13 +976,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>S202405007</v>
+        <v>S202405005</v>
       </c>
       <c r="B14" t="str">
         <v>比对通过</v>
       </c>
       <c r="C14" t="str">
-        <v>农药残留-拟除虫菊酯</v>
+        <v>重金属-铅</v>
       </c>
       <c r="D14" t="str">
         <v>合格</v>
@@ -1014,13 +1014,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>S202405008</v>
+        <v/>
       </c>
       <c r="B15" t="str">
-        <v>比对通过</v>
+        <v/>
       </c>
       <c r="C15" t="str">
-        <v>重金属-铅</v>
+        <v>农药残留-拟除虫菊酯</v>
       </c>
       <c r="D15" t="str">
         <v>合格</v>
@@ -1052,28 +1052,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>S202405006</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>比对不通过</v>
       </c>
       <c r="C16" t="str">
-        <v>重金属-镉</v>
+        <v>农药残留-有机磷</v>
       </c>
       <c r="D16" t="str">
-        <v>合格</v>
+        <v>不合格</v>
       </c>
       <c r="E16" t="str">
         <v>否</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>检测值超标</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>样品 S202405006 的 农药残留-有机磷 检测值超出标准范围</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>S202405007</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>比对通过</v>
       </c>
       <c r="C17" t="str">
-        <v>农药残留-有机磷</v>
+        <v>农药残留-拟除虫菊酯</v>
       </c>
       <c r="D17" t="str">
         <v>合格</v>
@@ -1128,45 +1128,159 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>S202405008</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>比对通过</v>
       </c>
       <c r="C18" t="str">
+        <v>重金属-铅</v>
+      </c>
+      <c r="D18" t="str">
+        <v>合格</v>
+      </c>
+      <c r="E18" t="str">
+        <v>否</v>
+      </c>
+      <c r="F18" t="str">
+        <v>报告撤回</v>
+      </c>
+      <c r="G18" t="str">
+        <v>样品 S202405008 的原报告已被撤回，需重新检测或补充材料</v>
+      </c>
+      <c r="H18" t="str">
+        <v>否</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>重金属-镉</v>
+      </c>
+      <c r="D19" t="str">
+        <v>合格</v>
+      </c>
+      <c r="E19" t="str">
+        <v>否</v>
+      </c>
+      <c r="F19" t="str">
+        <v>报告撤回</v>
+      </c>
+      <c r="G19" t="str">
+        <v>样品 S202405008 的 农药残留-有机磷 检测报告已被撤回</v>
+      </c>
+      <c r="H19" t="str">
+        <v>否</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>农药残留-有机磷</v>
+      </c>
+      <c r="D20" t="str">
+        <v>合格</v>
+      </c>
+      <c r="E20" t="str">
+        <v>否</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
         <v>农药残留-氨基甲酸酯</v>
       </c>
-      <c r="D18" t="str">
-        <v>合格</v>
-      </c>
-      <c r="E18" t="str">
-        <v>否</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
+      <c r="D21" t="str">
+        <v>合格</v>
+      </c>
+      <c r="E21" t="str">
+        <v>否</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/zy70922/output/report.xlsx
+++ b/zy70922/output/report.xlsx
@@ -410,7 +410,7 @@
         <v>对账ID</v>
       </c>
       <c r="B2" t="str">
-        <v>2d93a8a8-03f7-45d9-9558-de94c47b3444</v>
+        <v>20222baf-cd87-4b5e-a7cd-b2708677e46e</v>
       </c>
     </row>
     <row r="3">
@@ -418,7 +418,7 @@
         <v>生成时间</v>
       </c>
       <c r="B3" t="str">
-        <v>2026/5/27 00:39:13</v>
+        <v>2026/5/27 01:03:39</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>合格率</v>
       </c>
       <c r="B7" t="str">
-        <v>63%</v>
+        <v>75%</v>
       </c>
     </row>
     <row r="8">
@@ -466,7 +466,7 @@
         <v>待复核</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -553,7 +553,7 @@
         <v>所有检测项目合格，无差异，予以放行</v>
       </c>
       <c r="L2" t="str">
-        <v>2026/5/27 00:39:13</v>
+        <v>2026/5/27 01:03:39</v>
       </c>
     </row>
     <row r="3">
@@ -637,7 +637,7 @@
         <v>S202405002</v>
       </c>
       <c r="B5" t="str">
-        <v>比对不通过</v>
+        <v>比对通过</v>
       </c>
       <c r="C5" t="str">
         <v>农药残留-有机磷</v>
@@ -667,7 +667,7 @@
         <v>有机磷农药残留超标（0.08mg/kg &gt; 标准0.05mg/kg），需合作社提供农药使用记录并安排复检</v>
       </c>
       <c r="L5" t="str">
-        <v>2026/5/27 00:39:13</v>
+        <v>2026/5/27 01:03:39</v>
       </c>
     </row>
     <row r="6">
@@ -713,7 +713,7 @@
         <v>S202405003</v>
       </c>
       <c r="B7" t="str">
-        <v>比对不通过</v>
+        <v>比对通过</v>
       </c>
       <c r="C7" t="str">
         <v>重金属-铅</v>
@@ -743,7 +743,7 @@
         <v>复检超窗口原因为仪器故障维修，经质量负责人批准后予以放行。初检0.15mg/kg不合格，复检0.08mg/kg合格</v>
       </c>
       <c r="L7" t="str">
-        <v>2026/5/27 00:39:13</v>
+        <v>2026/5/27 01:03:39</v>
       </c>
     </row>
     <row r="8">
@@ -1131,7 +1131,7 @@
         <v>S202405008</v>
       </c>
       <c r="B18" t="str">
-        <v>比对通过</v>
+        <v>比对不通过</v>
       </c>
       <c r="C18" t="str">
         <v>重金属-铅</v>

--- a/zy70922/output/report.xlsx
+++ b/zy70922/output/report.xlsx
@@ -410,7 +410,7 @@
         <v>对账ID</v>
       </c>
       <c r="B2" t="str">
-        <v>20222baf-cd87-4b5e-a7cd-b2708677e46e</v>
+        <v>855ecd99-deed-4e8e-8b49-0bfd4507b598</v>
       </c>
     </row>
     <row r="3">
@@ -418,7 +418,7 @@
         <v>生成时间</v>
       </c>
       <c r="B3" t="str">
-        <v>2026/5/27 01:03:39</v>
+        <v>2026/5/27 01:10:24</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>合格率</v>
       </c>
       <c r="B7" t="str">
-        <v>75%</v>
+        <v>63%</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>S202405001</v>
       </c>
       <c r="B2" t="str">
-        <v>比对通过</v>
+        <v>已放行</v>
       </c>
       <c r="C2" t="str">
         <v>重金属-铅</v>
@@ -553,7 +553,7 @@
         <v>所有检测项目合格，无差异，予以放行</v>
       </c>
       <c r="L2" t="str">
-        <v>2026/5/27 01:03:39</v>
+        <v>2026/5/27 01:10:24</v>
       </c>
     </row>
     <row r="3">
@@ -637,7 +637,7 @@
         <v>S202405002</v>
       </c>
       <c r="B5" t="str">
-        <v>比对通过</v>
+        <v>需补材料</v>
       </c>
       <c r="C5" t="str">
         <v>农药残留-有机磷</v>
@@ -667,7 +667,7 @@
         <v>有机磷农药残留超标（0.08mg/kg &gt; 标准0.05mg/kg），需合作社提供农药使用记录并安排复检</v>
       </c>
       <c r="L5" t="str">
-        <v>2026/5/27 01:03:39</v>
+        <v>2026/5/27 01:10:24</v>
       </c>
     </row>
     <row r="6">
@@ -713,7 +713,7 @@
         <v>S202405003</v>
       </c>
       <c r="B7" t="str">
-        <v>比对通过</v>
+        <v>已放行</v>
       </c>
       <c r="C7" t="str">
         <v>重金属-铅</v>
@@ -743,7 +743,7 @@
         <v>复检超窗口原因为仪器故障维修，经质量负责人批准后予以放行。初检0.15mg/kg不合格，复检0.08mg/kg合格</v>
       </c>
       <c r="L7" t="str">
-        <v>2026/5/27 01:03:39</v>
+        <v>2026/5/27 01:10:24</v>
       </c>
     </row>
     <row r="8">

--- a/zy70922/output/report.xlsx
+++ b/zy70922/output/report.xlsx
@@ -410,7 +410,7 @@
         <v>对账ID</v>
       </c>
       <c r="B2" t="str">
-        <v>855ecd99-deed-4e8e-8b49-0bfd4507b598</v>
+        <v>a352618c-77aa-468e-9d24-6eade0fe9883</v>
       </c>
     </row>
     <row r="3">
@@ -418,7 +418,7 @@
         <v>生成时间</v>
       </c>
       <c r="B3" t="str">
-        <v>2026/5/27 01:10:24</v>
+        <v>2026/5/27 01:36:12</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>合格率</v>
       </c>
       <c r="B7" t="str">
-        <v>63%</v>
+        <v>75%</v>
       </c>
     </row>
     <row r="8">
@@ -458,7 +458,7 @@
         <v>已解决差异</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -466,7 +466,7 @@
         <v>待复核</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -553,7 +553,7 @@
         <v>所有检测项目合格，无差异，予以放行</v>
       </c>
       <c r="L2" t="str">
-        <v>2026/5/27 01:10:24</v>
+        <v>2026/5/27 01:36:12</v>
       </c>
     </row>
     <row r="3">
@@ -667,7 +667,7 @@
         <v>有机磷农药残留超标（0.08mg/kg &gt; 标准0.05mg/kg），需合作社提供农药使用记录并安排复检</v>
       </c>
       <c r="L5" t="str">
-        <v>2026/5/27 01:10:24</v>
+        <v>2026/5/27 01:36:12</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v>复检超窗口原因为仪器故障维修，经质量负责人批准后予以放行。初检0.15mg/kg不合格，复检0.08mg/kg合格</v>
       </c>
       <c r="L7" t="str">
-        <v>2026/5/27 01:10:24</v>
+        <v>2026/5/27 01:36:12</v>
       </c>
     </row>
     <row r="8">
@@ -1055,7 +1055,7 @@
         <v>S202405006</v>
       </c>
       <c r="B16" t="str">
-        <v>比对不通过</v>
+        <v>已放行</v>
       </c>
       <c r="C16" t="str">
         <v>农药残留-有机磷</v>
@@ -1073,19 +1073,19 @@
         <v>样品 S202405006 的 农药残留-有机磷 检测值超出标准范围</v>
       </c>
       <c r="H16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>放行</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>质量负责人李四</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>合作社提供完整农药使用记录，复检结果0.03mg/kg合格，予以放行</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>2026/5/27 01:36:12</v>
       </c>
     </row>
     <row r="17">
